--- a/PTBR/Lang/PTBR/Dialog/Drama/parttimer_jure.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/parttimer_jure.xlsx
@@ -415,13 +415,11 @@
 So, my friend… don’t let this chance slip through your fingers!</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Igreja de Jure está realizando uma campanha especial de conversão neste momento!  _x000D_
-_x000D_
-Mude de outro deus sem penalidades—e mais, seus dias de fé serão transferidos! E espere, tem mais! Por tempo limitado, você também receberá um travesseiro de corpo exclusivo de Jure totalmente de graça!  _x000D_
-_x000D_
-Então, meu amigo… não deixe essa chance escapar pelos seus dedos!  </t>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>A Igreja de Jure está com uma campanha especial de conversão agora!
+Troque de deus e não há penalidade: e seus dias de fé continuam valendo! E tem mais! Por tempo limitado, você também ganha uma almofada de corpo da Jure exclusiva, absolutamente grátis!
+Então, meu amigo… não deixe essa chance escapar!</t>
         </is>
       </c>
     </row>
@@ -449,9 +447,9 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim.  </t>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -479,9 +477,9 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não.  </t>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Não.</t>
         </is>
       </c>
     </row>
@@ -513,9 +511,9 @@
           <t>Okie, just making sure. Do you really want to convert your religion?</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ok, só para ter certeza. Você realmente quer mudar de religião?  </t>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Oki, só confirmando. Você quer mesmo trocar de religião?</t>
         </is>
       </c>
     </row>
@@ -543,9 +541,9 @@
           <t>Yes.</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sim.  </t>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Sim.</t>
         </is>
       </c>
     </row>
@@ -573,9 +571,9 @@
           <t>No.</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não.  </t>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Não.</t>
         </is>
       </c>
     </row>
@@ -600,9 +598,9 @@
           <t>Thanks! Phew, I just filled my daily quota.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Obrigado! Ufa, acabei de cumprir minha cota diária.  </t>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Valeu! Ufa, acabei de fechar minha cota do dia.</t>
         </is>
       </c>
     </row>
@@ -646,9 +644,9 @@
           <t>Shit!</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Droga!  </t>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>Merdas!</t>
         </is>
       </c>
     </row>
